--- a/Techniques/Correlation drift Detection/outputs/G11/dsas_g11_lubrication_system_correlation_detection/correlation_detection/dsas_g11_lubrication_correlation_detection_output3.xlsx
+++ b/Techniques/Correlation drift Detection/outputs/G11/dsas_g11_lubrication_system_correlation_detection/correlation_detection/dsas_g11_lubrication_correlation_detection_output3.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,25 +458,20 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Deviation Scribe Fault</t>
+          <t>Strength Score</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Strength Score</t>
+          <t>Strength Fault</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Strength Fault</t>
+          <t>RCA Suffocation</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>RCA Suffocation</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Root Cause</t>
         </is>
@@ -496,17 +491,14 @@
       <c r="E2" t="n">
         <v>6.814831106409888</v>
       </c>
-      <c r="F2" t="n">
-        <v>6.814831106409888</v>
-      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -522,17 +514,14 @@
       <c r="E3" t="n">
         <v>0.01797232797738467</v>
       </c>
-      <c r="F3" t="n">
-        <v>0.01797232797738467</v>
-      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -548,17 +537,14 @@
       <c r="E4" t="n">
         <v>1.73976336204625</v>
       </c>
-      <c r="F4" t="n">
-        <v>1.73976336204625</v>
-      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -574,17 +560,14 @@
       <c r="E5" t="n">
         <v>4.085804866406339</v>
       </c>
-      <c r="F5" t="n">
-        <v>4.085804866406339</v>
-      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -600,17 +583,14 @@
       <c r="E6" t="n">
         <v>3.54038569471587</v>
       </c>
-      <c r="F6" t="n">
-        <v>3.54038569471587</v>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -626,17 +606,14 @@
       <c r="E7" t="n">
         <v>0.287707208504877</v>
       </c>
-      <c r="F7" t="n">
-        <v>0.287707208504877</v>
-      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -652,17 +629,14 @@
       <c r="E8" t="n">
         <v>0.9671147163520648</v>
       </c>
-      <c r="F8" t="n">
-        <v>0.9671147163520648</v>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -678,17 +652,14 @@
       <c r="E9" t="n">
         <v>0.004760185968228706</v>
       </c>
-      <c r="F9" t="n">
-        <v>0.004760185968228706</v>
-      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -704,17 +675,14 @@
       <c r="E10" t="n">
         <v>0</v>
       </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -730,17 +698,14 @@
       <c r="E11" t="n">
         <v>0.1160699084986323</v>
       </c>
-      <c r="F11" t="n">
-        <v>0.1160699084986323</v>
-      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -756,17 +721,14 @@
       <c r="E12" t="n">
         <v>1.96262303988198</v>
       </c>
-      <c r="F12" t="n">
-        <v>1.96262303988198</v>
-      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
